--- a/important_mails_2026-07-05.xlsx
+++ b/important_mails_2026-07-05.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1186,7 +1186,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1201,122 +1201,21 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sun, 28 Jun 2026 14:57:16 +0000</t>
+          <t>Fri, 3 Jul 2026 14:39:15 +0000</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID H7OQM8penQ
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 29, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-1724036457613526</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 28 Jun 2026 14:55:52 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Balance paid on your Amazon seller account</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon Services.
- We have charged your credit card for $81.22 in an attempt to settle your Amazon seller account balance.
- Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
- You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
- Thank you for selling on Amazon.
- Amazon Services
- Help us improve your experience on selling on Amazon through this brief survey:
- https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202606281349
- Was this email helpful?
- SPC-USAmazon-510175622387886</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 3 Jul 2026 14:39:15 +0000</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1333,39 +1232,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 10:10:03 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -1389,39 +1288,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 17:09:13 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Access your January–March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1437,39 +1336,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 16:54:53 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Access your January - March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1485,39 +1384,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1537,39 +1436,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:43:29 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1586,39 +1485,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:42:06 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1638,39 +1537,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:21:30 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1690,39 +1589,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1739,40 +1638,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 06:41:28 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -1787,39 +1686,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:09:44 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant is now live in France, Italy &amp; Spain</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  AI-powered assistance is now available in Seller Central to help you manage your business more efficiently.
@@ -1837,40 +1736,40 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 13:15:52 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>The Amazon Accelerate 2026 speaker lineup is here! Register now to
  save $100</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49sbm/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z49sbq/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
@@ -1887,40 +1786,40 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:09:19 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -1932,39 +1831,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:26:45 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>El Asistente de vendedores ya está activo en Francia, Italia y España</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  La asistencia con tecnología de IA ya está disponible en Seller Central para ayudarte a gestionar tu negocio de forma más eficiente.
@@ -1978,39 +1877,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:11:01 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -2028,39 +1927,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 13:49:18 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>L'assistente venditori è ora attivo in Francia, Italia e Spagna</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  L'assistenza basata su AI è ora disponibile in Seller Central per aiutarti a gestire la tua attività in modo più efficiente.
@@ -2075,39 +1974,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:04:35 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Presentar información de cumplimiento normativo de la RAP en Portugal</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  La normativa portuguesa sobre la RAP se aplica a los productos vendidos a clientes de Portugal.
@@ -2124,39 +2023,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 02:53:05 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 06/2026</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -2174,39 +2073,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 00:26:34 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;
@@ -2221,39 +2120,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:10:24 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -2269,39 +2168,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 04:34:30 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2325,39 +2224,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:35:02 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2380,39 +2279,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:23:13 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2433,39 +2332,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 00:16:50 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
@@ -2492,6 +2391,107 @@
 - Reduce contact and return rates
  Follow these practices to prevent customer confusion and minimize your workload:
 - Monitor the Response Needed inbox within the Buyer-Seller Messaging Service . In the rare case that we need your he</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 28 Jun 2026 14:57:16 +0000</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID H7OQM8penQ
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on June 29, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-1724036457613526</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 28 Jun 2026 14:55:52 +0000</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Balance paid on your Amazon seller account</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card for $81.22 in an attempt to settle your Amazon seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
+ Thank you for selling on Amazon.
+ Amazon Services
+ Help us improve your experience on selling on Amazon through this brief survey:
+ https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202606281349
+ Was this email helpful?
+ SPC-USAmazon-510175622387886</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -8076,173 +8076,21 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Fri, 5 Jun 2026 03:06:03 +0000</t>
+          <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory</t>
+          <t>Votre paiement est en cours</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-You recently received a notice about the removal of your listing(s) for the product(s) listed below.
-You were required to submit a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing within 30 days of the notification sent on 05/04/2026. Since a removal order was not submitted since the notification was sent, we have submitted a disposal order for this inventory in accordance with FBA policies.
-For more information regarding the restriction of this product, see the notification e-mail you received from Product Safety. If you have additional questions, please contact Seller Support.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0DRTR7GYJ
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_PRODUCT_REMOVAL_ORDER_CREATED
-SPC-USAmazon-492583426128753</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 19:23:36 +0000</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 19:17:04 +0000</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>Votre paiement est en cours</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8257,39 +8105,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:07:09 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -8317,39 +8165,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 22:31:41 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para julio</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para julio
@@ -8378,39 +8226,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:42 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Łącze do zaktualizowanego raportu podatkowego dotyczącego Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Ponownie przesyłamy kwartalny raport podatkowy, który obejmuje dane takie jak informacje o tożsamości, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -8428,39 +8276,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 10:01:00 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8479,39 +8327,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:26 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -8525,39 +8373,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 00:26:49 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;
@@ -8572,39 +8420,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 09:29:52 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Prime会员日明天开始：最后提报促销活动的机会</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -8628,39 +8476,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8675,39 +8523,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 10:18:43 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8728,39 +8576,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 10:02:13 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>最后机会：请于6月19日前提报 Prime Day 促销</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -8783,39 +8631,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 14:18:31 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -8835,39 +8683,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:14:39 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Soumettre les numéros d'enregistrement REP avant le 30 juin</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -8876,39 +8724,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 09:11:12 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Seller News: June 2026</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -8928,40 +8776,40 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 17:13:19 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Get increased New Selection Program (2026) benefits starting July
  30</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
  Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
@@ -8975,39 +8823,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 00:29:05 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;
@@ -9023,39 +8871,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:26:46 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9070,39 +8918,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:13:30 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -9119,39 +8967,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:43 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -9169,40 +9017,40 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:12 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -9220,39 +9068,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:08:19 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -9270,39 +9118,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:17:27 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -9341,39 +9189,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:32 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -9391,39 +9239,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:13 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, xiao jianming:
@@ -9441,40 +9289,40 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:15:21 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -9492,39 +9340,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:24 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Documents de sécurité des produits requis pour les garder actifs</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour xiao jianming,
@@ -9542,39 +9390,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:34:40 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -9589,39 +9437,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 17:10:30 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -9639,40 +9487,40 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 04:55:50 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Hemos actualizado los requisitos del distintivo de Prime para Prime
  Day</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  Para ayudarte a mantener el distintivo de Prime durante Prime Day, hemos actualizado nuestros requisitos del distintivo en España.
@@ -9693,39 +9541,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:49:02 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -9747,39 +9595,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:44:43 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -9799,39 +9647,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:35:25 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Mise à jour du statut des matières dangereuses (Hazmat)</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>96
  Mise à jour du statut des matières dangereuses (Hazmat)
@@ -9843,39 +9691,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:03:25 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -9887,39 +9735,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:03:17 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Update van status gevaarlijke goederen</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>96
  Update van status gevaarlijke goederen
@@ -9941,39 +9789,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:41:38 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>"Pereira, Sheryl" &lt;persher@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Amazon India your next growth market</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>Hi Team,
 Sheryl this side from Amazon India Out of Country team, we work with high-potential global brands to successfully launch and scale their presence in India. Given the current selection gaps and growing customer demand, I believe Amazon.in could be a great opportunity for Roaxkois
@@ -9987,39 +9835,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 08:25:43 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -10047,39 +9895,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:16:28 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>27 lipca rozpocznie się ulepszanie tytułów stron produktów</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>96
  Tytuły we wszystkich kategoriach (z wyjątkiem kategorii „Media”) będą musiały zawierać 75 znaków lub mniej, łącznie ze spacjami. Nowa funkcja „Najważniejsze informacje” zapewnia dodatkowe 125 znaków, umożliwiając udostępnianie materiałów.
@@ -10090,40 +9938,40 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:08:24 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti per migliorare i titoli dei prodotti a partire dal 27
  luglio</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>96
  I titoli in tutte le categorie eccetto i prodotti multimediali dovranno contenere un massimo di 75 caratteri, spazi inclusi. Nelle caratteristiche principali dei prodotti, saranno ora disponibili altri 125 caratteri per descrivere i materiali.
@@ -10134,39 +9982,39 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:05:34 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Updates om je producttitels te verbeteren beginnen op 27 juli</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>96
  Titels in alle categorieën, behalve in de categorie ‘media’ mogen maximaal 75 tekens lang zijn, inclusief spaties. Met de nieuwe functie Itemhoogtepunten kun je nu 125 extra tekens gebruiken om materiaal te delen.
@@ -10178,39 +10026,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:05:16 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Las actualizaciones para mejorar los títulos de los productos entrarán en vigor el 27 de julio</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Los títulos de todas las categorías, excepto multimedia, tendrán que tener 75 caracteres o menos, contando espacios. La nueva herramienta de aspectos destacados del producto ahora ofrece 125 caracteres más para compartir materiales.
@@ -10221,39 +10069,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:10:59 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Nueva restricción de la UE sobre la puesta de inventario de productos textiles y calzado a disposición de Amazon</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>96
  A más tardar el 19 de julio, actualiza la configuración de retiradas de prendas de vestir y calzado en los centros logísticos de la UE
@@ -10266,40 +10114,40 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:03:48 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Nuove limitazioni dell'Unione europea sul reimpiego di prodotti
  tessili e calzature</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiorna le impostazioni di rimozione per capi di abbigliamento, accessori e calzature nei centri logistici dell'Unione europea entro il 19 luglio
@@ -10312,39 +10160,39 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:26:32 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Nowe ograniczenia UE dotyczące usuwania tekstyliów i obuwia</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Do 19 lipca zmień ustawienia wycofywania zapasów odzieży i obuwia magazynowanych w centrach logistycznych w UE
@@ -10358,39 +10206,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:08:34 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Nouvelle restriction de l’UE sur la mise au rebut des textiles et des chaussures</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>96
  D’ici le 19 juillet, mettez à jour vos paramètres de demande de prélèvement pour les vêtements, les accessoires vestimentaires et les chaussures dans les centres de distribution de l’UE
@@ -10403,39 +10251,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 15:18:50 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -10457,39 +10305,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:50:24 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Statusuppdatering för farligt gods</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>96
  Statusuppdatering för farligt gods
@@ -10511,39 +10359,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:16:55 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -10564,39 +10412,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:10:30 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -10617,39 +10465,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:05:17 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -10671,39 +10519,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:05:00 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Update van status gevaarlijke goederen</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>96
  Update van status gevaarlijke goederen
@@ -10725,39 +10573,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 19:32:37 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 5/2026
  96
@@ -10780,39 +10628,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 08:39:32 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Versand durch Amazon for 5/2026
  96
@@ -10836,39 +10684,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 07:48:24 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -10895,39 +10743,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:51:17 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 5/2026</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 5/2026
  96
@@ -10954,39 +10802,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:47:21 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 5/2026
  96
@@ -11006,39 +10854,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:42:19 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 5/2026</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 5/2026
  96
@@ -11065,39 +10913,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:15:01 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 5/2026</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Verkäufer for 5/2026
  96
@@ -11121,39 +10969,39 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:12:39 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Korygująca Sprzedawcy for 5/2026</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Korygująca Sprzedawcy for 5/2026
  96
@@ -11177,39 +11025,39 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:57:10 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 5/2026</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 5/2026
  96
@@ -11227,39 +11075,39 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:54:32 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 5/2026
  96
@@ -11283,39 +11131,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:42:06 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 5/2026
  96
@@ -11338,39 +11186,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:59 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -11385,39 +11233,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:01:19 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -11435,39 +11283,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 12:36:48 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -11494,39 +11342,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 12:31:12 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -11553,39 +11401,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:43:20 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -11610,39 +11458,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:38:16 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -11667,39 +11515,39 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:25:17 +0000</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -11726,39 +11574,39 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:21:01 +0000</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -11783,39 +11631,39 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:10:07 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -11842,39 +11690,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 10:55:24 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026
  96
@@ -11893,39 +11741,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 10:25:16 +0000</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026
  96
@@ -11944,39 +11792,39 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 09:33:20 +0000</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -12000,39 +11848,39 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 07:52:40 +0000</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 5/2026
  96
@@ -12056,39 +11904,39 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 07:36:30 +0000</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -12115,39 +11963,39 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:48:36 +0000</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -12171,39 +12019,39 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:24:07 +0000</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 5/2026</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 5/2026
  96
@@ -12228,39 +12076,39 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:01:50 +0000</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 5/2026
  96
@@ -12285,39 +12133,39 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:56:14 +0000</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 5/2026
  96
@@ -12335,39 +12183,39 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:28:55 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 5/2026</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 5/2026
  96
@@ -12394,39 +12242,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:23:44 +0000</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 5/2026
  96
@@ -12444,39 +12292,39 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:10:53 +0000</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 5/2026</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 5/2026
  96
@@ -12501,39 +12349,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:02:43 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 5/2026</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 5/2026
  96
@@ -12560,39 +12408,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 04:45:31 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 5/2026
  96
@@ -12613,802 +12461,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 5 Jun 2026 13:05:07 +0000</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>最大化您的 Prime Day 业绩</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
-        <is>
-          <t>最大化您的 Prime Day 业绩
-尊敬的卖家，
-为 2026 年 Prime Day做好准备 - 为数百万 Prime 会员打造不容错过的优惠！加入我们今年6月为期4天活动。通过提交促销，确保充足库存，提升曝光度以助力您冲刺最佳业绩！
-关键日期
-活动日期： 2026年6月 (具体日期待公布)
-提报截止日期： 促销 – 2026 年 6 月 19 日，价格折扣 – 活动结束前 12 小时
-FBA入仓截止日期：
-欧盟 – 2026年5月27日，英国 – 2026年6月5日
-提报您的促销 &gt; https://go.amazonsellerservices.com/e/229492/reate-ld-DC-EM-D461067421-Wk23/7z3srtt/6697298646/h/rMvopgR4Nl_0V-drvJKtpkn_-lVTBROzyCraVQvBh5o
-&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="section" role="presentation" style="width:100%;"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td align="center"&gt;
-			&lt;div role="none"&gt;
-&lt;!--[if(mso)|(IE)]&gt;
-&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="block-grid-outlook" style="width:600px;" width="600" &gt;
-&lt;tr&gt;
-&lt;td style="line-height:0px;font-size:0px;mso-line-height-rule:exactly;"&gt;&lt;![endif]--&gt;
-			&lt;div style="margin:0 auto;border-radius:0px;max-width:600px;"&gt;
-			&lt;table align="center" border="0" cellpadding="0" cellspacing="0" role="presentation" style="width:100%;border-radius:0px;"&gt;
-				&lt;tbody&gt;
-					&lt;tr&gt;
-						&lt;td class="block-grid" style="border-radius:0px;font-size:0px;padding:12px 0px 12px 0px;text-align:center;vertical-align:top;"&gt;
-&lt;!--[if(mso)|(IE)]&gt;
-&lt;table role="presentati</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 5 Jun 2026 12:43:35 +0000</t>
-        </is>
-      </c>
-      <c r="E239" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F239" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
-        </is>
-      </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
- 96
-Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 5.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de
- Ein Problem mit dieser E-Mail melden
- Bei Fragen besuchen Sie: Seller Central
- Zum Ändern Ihrer E-Mail-Einstellungen, gehen Sie zu: Benachrichtigungseinstellungen
- Wir hoffen, diese Nachricht ist hilfreich für Sie. Falls Sie allerdings in Zukunft keine E-Mails dieser Art von Amazon.de erhalten möchten, melden Sie sich bitte ab.
- Copyright 2026 Amazon Inc. oder Tochtergesellschaften. Alle Rechte vorbehalten.
- Amazon EU S.à r.l.
-38 avenue John F. Kennedy,
-L-1855 Luxemburg,
-Handelsregisternummer Luxemburg: B-101818,
- Gesellschaftskapital: 165.833 EUR,
-Gewer</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 5 Jun 2026 12:33:36 +0000</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F240" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
-        </is>
-      </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
- 96
-Hej Shen zhen shi wei hai zhong xin ke ji you xian!
-Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 5/2026 nu finns tillgänglig på ditt Seller Central-konto.
-För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
-På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
-Om du har några frågor, kontakta säljarsupport.
-Vänliga hälsningar,
-Amazon.se
- Rapportera ett problem med detta e-post
- Om du har några frågor besök: Seller Central
- För att ändra dina e-postinställningar, besök: Inställningar för meddelanden
- Vi hoppas att du tyckte att det här meddelandet var användbart. Om du föredrar att inte få framtida e-postmeddelanden av detta slag från Amazon.com, välj bort det här.
- Upphovsrätt 2026 Amazon, Inc, eller dess dotterbolag. Alla rättigheter förbehållna.
- Amazon EU S.à r.l.
-38 avenue John F. Kennedy
-L-1855 Luxemburg
-Registrerat i Luxemburg No. B-101818
-Aktiekapital 165 833 EUR
-Företagets registreringsnummer: 134248
-Momsregistrering för Luxemburg LU 20260743.
- SPC-EU</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 5 Jun 2026 12:16:55 +0000</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F241" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026</t>
-        </is>
-      </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026
- 96
-Hello,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 5/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Tax Document Library . In your Tax Document Library, you will be able to view, download or print your invoice.
-The Amazon Services Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- We hope you found this message to be useful. However, if you'd rather not receive future e-mails of this sort from Amazon.com, please opt-out here.
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-EUAmazon-2058287427615275</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 5 Jun 2026 12:09:15 +0000</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F242" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026</t>
-        </is>
-      </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026
- 96
-Hello,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 5/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Tax Document Library . In your Tax Document Library, you will be able to view, download or print your invoice.
-The Amazon Services Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- We hope you found this message to be useful. However, if you'd rather not receive future e-mails of this sort from Amazon.com, please opt-out here.
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-EUAmazon-2075879615395517</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 5 Jun 2026 12:09:08 +0000</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F243" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
-        </is>
-      </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
- 96
-Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 5 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.nl
- Rapporteer een probleem met deze e-mail
- Als je vragen hebt, ga je naar: Seller Central
- Om je e-mailvoorkeuren te wijzigen, ga je naar: Voorkeuren voor meldingen
- We hopen dat je iets aan dit bericht hebt gehad. Als je in de toekomst echter liever niet meer van dit soort e-mails van Amazon.com wilt ontvangen, kun je je afmelden hier.
- Auteursrecht (copyright) 2026 Amazon, Inc. of haar dochterondernemingen. Alle rechten voorbehouden.
- Amazon Services Europe S.à r.l.
-38 avenue John F. Kennedy
-L-1855 Luxemburg
-Geregistreerd in Luxemburg
-RCS L</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 5 Jun 2026 11:58:55 +0000</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F244" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
- 96
-Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 5.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de
- Ein Problem mit dieser E-Mail melden
- Bei Fragen besuchen Sie: Seller Central
- Zum Ändern Ihrer E-Mail-Einstellungen, gehen Sie zu: Benachrichtigungseinstellungen
- Wir hoffen, diese Nachricht ist hilfreich für Sie. Falls Sie allerdings in Zukunft keine E-Mails dieser Art von Amazon.de erhalten möchten, melden Sie sich bitte ab.
- Copyright 2026 Amazon Inc. oder Tochtergesellschaften. Alle Rechte vorbehalten.
- Amazon EU S.à r.l.
-38 avenue John F. Kennedy,
-L-1855 Luxemburg,
-Handelsregisternummer Luxemburg: B-101818,
- Gesellschaftskapital: 165.833 EUR,
-Gewer</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 5 Jun 2026 11:38:44 +0000</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F245" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
-        </is>
-      </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.es Factura Logística de Amazon for 5/2026
- 96
-Hola, Shen zhen shi wei hai zhong xin ke ji you xian:
-Te escribimos para comunicarte que tu Factura Logística de Amazon del mes de 5/2026 ya está disponible en tu cuenta de Seller Central.
-Para acceder a la factura, ve a Seller Central &gt; Informes &gt; Biblioteca de documentos fiscales &gt; Facturas de tarifas aplicables al vendedor.
-Allí podrás ver, descargar o imprimir tu factura.
-Para consultas, contacta con atención al vendedor.
-Atentamente,
-Amazon.es
- Informar de un problema con este correo electrónico
- Si tienes alguna pregunta, visita: Seller Central
- Para cambiar sus preferencias de correo electrónico visitan: Preferencias de Notificación
- Esperamos que este mensaje te haya parecido útil. Sin embargo, si prefieres no recibir correos electrónicos de Amazon.es de este tipo en el futuro, haz clic aquí.
- Copyright 2026 Amazon.com.mx, Inc. o sus afiliados. Todos los derechos reservados.
- Amazon EU S.à r.l.
-38 avenue John F. Kennedy,
-L-1855 Luxemburgo,
-Número de Registro en Luxemburgo: No. B-101818,
-Capital Social 165.833 EUR,
-Número de licencia de actividad: 134248,
-Nº de Registro IVA en Luxemburgo: LU 20260743.
- SPC-EUAmazon-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 23:11:17 +0000</t>
-        </is>
-      </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F246" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
- le offerte</t>
-        </is>
-      </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
-        <is>
-          <t>96
- Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 23:10:46 +0000</t>
-        </is>
-      </c>
-      <c r="E247" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F247" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
- opnieuw te activeren</t>
-        </is>
-      </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
- Hallo Weihai EU,
- Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 19:37:38 +0000</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F248" s="2" t="inlineStr">
-        <is>
-          <t>提交商品安全文件以重新启售商品</t>
-        </is>
-      </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
-        <is>
-          <t>96
- 提交商品安全文件以重新启售商品
- 尊敬的 Weihai EU：
-您好！
- 您的部分商品因缺少必要的商品合规信息而被停售。查看下面的详细信息和后续步骤。受影响的商品显示在此电子邮件的末尾。
- 为什么会发生这种情况？
- 我们之所以采取此措施，是因为这些商品缺少必要的合规信息。请查看我们的 商品安全与合规 帮助页面，了解有关适用法律法规和亚马逊政策的信息。为了确定此问题，我们综合运用了自动化技术和专家人工评审，最终做出这一决定。
- 此电子邮件末尾的表格提供了特定于商品的合规性要求。
- 如何重新启售商品？
- 要提供所需的合规信息，请前往 账户状况 页面并找到商品合规性请求：
--
- 如果您有所需的文件，请按照相关说明提交您的合规文件。我们仅会重新启售满足合规要求的商品。
--
- 如果您认为您的商品无需遵守这些要求，请提交相关文件，说明它们为何不受这些合规要求的约束。
- 有关分步操作说明，请参阅 提交合规文件或对文件请求提出申诉 帮助页面。
- 为避免进一步影响您的账户，请停售或删除您不打算销售或申诉的任何不合规商品。
- 如果我未执行上述操作，会怎么样？
- 如果您未提供所需的合规信息，则受影响的 ASIN 将一直处于停售状态，直到您或其他发布此商品的销售伙伴满足合规要求。
- 这些商品的亚马逊物流库存会怎样？
- 您必须在收到本通知后的 30 天内从我们的运营中心移除这些商品。如果未移除，我们将按照《亚马逊服务商业解决方案协议》中的规定弃置此库存，并且费用由您承担。要了解如何移除库存，请参阅 移除库存 帮助页面。
- 我们愿意随时为您提供帮助。
- 有关更多信息，请观看卖家大学中的 安全与合规简介 视频
- 如果您有其他问题，请在您的 账户状况 控制面板上提交请求。
- 亚马逊商品安全与合规性
- 受影响的商品
- 详情
- Roaxkois Töpferset für Kinder, Töpferset für Zuhause mit ton lufttrocknend, Töpferscheibe Elektrisch, Diamant Aufkleber, Kreativ Set für Kinder, Geschenk-Ideen, Geschenk für Mädchen Jungen
- ASIN： B0DL3PC2WS
- 亚马逊要求您证明自己在亚马逊德国站上架的儿童玩具符合适用的法律、法规、标准和亚马逊政策。
-要销售儿童玩具，您必须满足 儿童玩具帮助页面 上列出的要求，并与我们的合作伙伴第三方测试、检验和认证 (TIC) 服务提供商合作，验证您的商品符合这些要求。
-儿童玩具是指供14岁或以下儿童在学习或玩耍时使用的商品。
-亚马逊根据以下标准来确定商品是否为“儿童玩具”：
-商品包装上的年龄分级标明该玩具专供 14 岁或以下儿童使用。
-产品的包装、展示、促销或广告显示该产品适</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 19:31:54 +0000</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F249" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
-        </is>
-      </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
-        <is>
-          <t>96
- Presenta la documentación sobre seguridad del producto para reactivar los listings
- Hola, Weihai EU:
- Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 19:14:06 +0000</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F250" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
-        <is>
-          <t>96
- Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 19:10:02 +0000</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
-        </is>
-      </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
-        <is>
-          <t>96
- Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
- Bonjour Weihai EU,
- Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructio</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:46:44 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13432,39 +12517,39 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:45:39 +0000</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13488,39 +12573,39 @@
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 03:25:54 +0000</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-09</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13542,39 +12627,39 @@
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:59:29 +0000</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13598,39 +12683,39 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 03:24:34 +0000</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-02</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13652,39 +12737,39 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 04:57:38 +0000</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-25</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13706,39 +12791,39 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 04:53:34 +0000</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-25</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr"/>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13762,39 +12847,39 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 04:38:11 +0000</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13818,39 +12903,39 @@
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 03:47:37 +0000</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-18</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13874,39 +12959,39 @@
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 12:14:25 +0000</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Connect with an Amazon expert at Seller Café—Save $100 with early-bird pricing</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z46y96/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/4uHYwMZ-ld-EM/7z46y99/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
@@ -13922,39 +13007,39 @@
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 03:04:08 +0000</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Action Required: Transparency Barcode Required for Your Products</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello from Amazon Seller Services,
@@ -13970,39 +13055,39 @@
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 08:49:28 +0000</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>"Gao, Mark" &lt;gaomark@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>亚马逊广告限时激励活动 - Weihai EU</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>Amazon has replaced the attachment in this email with download link.
 Important: This link may contain content that is confidential. Please exercise appropriate caution when sharing.
@@ -14030,39 +13115,39 @@
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:43:31 +0000</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -14084,39 +13169,39 @@
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:43:28 +0000</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -14138,39 +13223,39 @@
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:03:54 +0000</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>You have until July 17 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr"/>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -14179,39 +13264,39 @@
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:33:42 +0000</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except for media will need to be 75 characters or less including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
@@ -14223,39 +13308,39 @@
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:07:52 +0000</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except media will need to be 75 characters or less, including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
@@ -14267,39 +13352,39 @@
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 20:04:50 +0000</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except for media will need to be 75 characters or less including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
@@ -14311,39 +13396,39 @@
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:18:13 +0000</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Updates to improve your product titles begin on July 27</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr"/>
-      <c r="H270" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>96
  Titles in all categories except for media will need to be 75 characters or less, including spaces. A new item highlights feature now provides an additional 125 characters for sharing materials.
@@ -14355,39 +13440,39 @@
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 14:50:02 +0000</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Earn up to €240 per shipment with C2S2 PCP Pallets</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3yyjt/6708104655/h/1UCuxAj2NkD65NTovD-vcIwWERBh1hVRp_O_epQxzho)
 C2S2 PCP Pallet Spring Promotion: Ship More, Save More
@@ -14409,39 +13494,39 @@
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 11:06:34 +0000</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon stranded inventory &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Review stranded inventory scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Fix stranded inventory
@@ -14458,39 +13543,39 @@
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:46:42 +0000</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Mise à jour du statut de matières dangereuses</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>96
  Mise à jour du statut de matières dangereuses
@@ -14511,39 +13596,39 @@
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:07:01 +0000</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -14566,39 +13651,39 @@
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 01:06:59 +0000</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -14622,39 +13707,39 @@
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 07:30:07 +0000</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>transparency-queue &lt;transparency-queue@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>成功进行 OPR 评估所需采取的措施</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>尊敬的Transparency(透明计划)客户：
 您好！感谢您在Transparency(透明计划)中注册您的商品。
